--- a/Movimientos/Operaciones202605.xlsx
+++ b/Movimientos/Operaciones202605.xlsx
@@ -8,30 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\red\POWER BI\Movimientos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D5CDD29C-9115-4F85-AC73-8D7AE1F0AFB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{51B87E81-405D-449A-8DE2-866E65E09EA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17300" yWindow="2100" windowWidth="14400" windowHeight="8250" xr2:uid="{E9C56F18-CA01-4CE1-B2AA-D0E692F77484}"/>
+    <workbookView xWindow="17760" yWindow="2560" windowWidth="14400" windowHeight="8250" xr2:uid="{ADFCEAA9-6A6E-4312-B294-4C4B8A6326AA}"/>
   </bookViews>
   <sheets>
     <sheet name="Operacio" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7433" uniqueCount="909">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8105" uniqueCount="970">
   <si>
     <t>NOM_EMPR</t>
   </si>
@@ -2670,27 +2659,114 @@
     <t xml:space="preserve">Coina PN                           </t>
   </si>
   <si>
+    <t>030271</t>
+  </si>
+  <si>
+    <t>1100</t>
+  </si>
+  <si>
+    <t>030272</t>
+  </si>
+  <si>
+    <t>1549</t>
+  </si>
+  <si>
+    <t>012093</t>
+  </si>
+  <si>
+    <t>0626</t>
+  </si>
+  <si>
+    <t>012094</t>
+  </si>
+  <si>
+    <t>1021</t>
+  </si>
+  <si>
+    <t>012095</t>
+  </si>
+  <si>
+    <t>1040</t>
+  </si>
+  <si>
+    <t>1172746</t>
+  </si>
+  <si>
     <t>20260510</t>
   </si>
   <si>
     <t>2331</t>
   </si>
   <si>
-    <t>E.S. ALMONTE,S.</t>
-  </si>
-  <si>
-    <t>E ROCIANA, 5</t>
+    <t>E.S. ALMONTE,S.L. CT</t>
+  </si>
+  <si>
+    <t>ALMONTE</t>
   </si>
   <si>
     <t>001,695</t>
   </si>
   <si>
+    <t>1578474</t>
+  </si>
+  <si>
+    <t>20260511</t>
+  </si>
+  <si>
+    <t>1731</t>
+  </si>
+  <si>
+    <t>001,759</t>
+  </si>
+  <si>
+    <t>0070431094076401160</t>
+  </si>
+  <si>
+    <t>6861-LBR</t>
+  </si>
+  <si>
+    <t>1947559</t>
+  </si>
+  <si>
+    <t>ASISTENCIA TÉCNICA I</t>
+  </si>
+  <si>
+    <t>AMPOSTA</t>
+  </si>
+  <si>
+    <t>ITV</t>
+  </si>
+  <si>
+    <t>001</t>
+  </si>
+  <si>
+    <t>000662</t>
+  </si>
+  <si>
+    <t>0110</t>
+  </si>
+  <si>
+    <t>000663</t>
+  </si>
+  <si>
+    <t>1015</t>
+  </si>
+  <si>
+    <t>1221590</t>
+  </si>
+  <si>
+    <t>1147</t>
+  </si>
+  <si>
+    <t>EL BRUC</t>
+  </si>
+  <si>
+    <t>001,778</t>
+  </si>
+  <si>
     <t>0070431094076400626</t>
   </si>
   <si>
-    <t>20260511</t>
-  </si>
-  <si>
     <t>0013</t>
   </si>
   <si>
@@ -2721,9 +2797,6 @@
     <t>A H-624 VARIANT</t>
   </si>
   <si>
-    <t>001,759</t>
-  </si>
-  <si>
     <t>1049</t>
   </si>
   <si>
@@ -2748,16 +2821,115 @@
     <t>E.S. ADEMUZ C-3</t>
   </si>
   <si>
-    <t>1147</t>
-  </si>
-  <si>
-    <t>E.S. EL BRUCH S</t>
-  </si>
-  <si>
-    <t>KM 567</t>
-  </si>
-  <si>
-    <t>001,778</t>
+    <t>CARBURANTE SAGU</t>
+  </si>
+  <si>
+    <t>CTRA.VALENCIA-B</t>
+  </si>
+  <si>
+    <t>1533</t>
+  </si>
+  <si>
+    <t>E.S. CHUCENA NO</t>
+  </si>
+  <si>
+    <t>PK 37</t>
+  </si>
+  <si>
+    <t>E.S.CHUCENA SUR</t>
+  </si>
+  <si>
+    <t>K 37</t>
+  </si>
+  <si>
+    <t>20260512</t>
+  </si>
+  <si>
+    <t>0625</t>
+  </si>
+  <si>
+    <t>ES COMBUSTIBLES</t>
+  </si>
+  <si>
+    <t>RI CR-503 P.K.</t>
+  </si>
+  <si>
+    <t>0735</t>
+  </si>
+  <si>
+    <t>E.S. RAUSAN, S.</t>
+  </si>
+  <si>
+    <t>-II, PK-341</t>
+  </si>
+  <si>
+    <t>001,719</t>
+  </si>
+  <si>
+    <t>0759</t>
+  </si>
+  <si>
+    <t>E.S.CARTAYA SIE</t>
+  </si>
+  <si>
+    <t>9 PK 102 MD</t>
+  </si>
+  <si>
+    <t>001,745</t>
+  </si>
+  <si>
+    <t>0919</t>
+  </si>
+  <si>
+    <t>LOS POTROS CTRA</t>
+  </si>
+  <si>
+    <t>7,7</t>
+  </si>
+  <si>
+    <t>0927</t>
+  </si>
+  <si>
+    <t>COMBUSTIBLES PL</t>
+  </si>
+  <si>
+    <t>R, AUTOVIA A-66</t>
+  </si>
+  <si>
+    <t>0938</t>
+  </si>
+  <si>
+    <t>E.S. J. CARRION</t>
+  </si>
+  <si>
+    <t>EDITERRANEO E-1</t>
+  </si>
+  <si>
+    <t>001,749</t>
+  </si>
+  <si>
+    <t>ES PINSEQUE-ZOI</t>
+  </si>
+  <si>
+    <t>A. A-68, PK.258</t>
+  </si>
+  <si>
+    <t>0070431094076400642</t>
+  </si>
+  <si>
+    <t>0951</t>
+  </si>
+  <si>
+    <t>LES 4 RODES, S.</t>
+  </si>
+  <si>
+    <t>.61</t>
+  </si>
+  <si>
+    <t>001,100</t>
+  </si>
+  <si>
+    <t>001,709</t>
   </si>
 </sst>
 </file>
@@ -2844,12 +3016,12 @@
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="NumericoDerecha" xfId="3" xr:uid="{F8121386-6F89-4771-9540-FD77CB9BDB98}"/>
-    <cellStyle name="NumericoDerechaCuatroDecimales" xfId="5" xr:uid="{E91B7400-9F48-48CC-B3F1-43D0AB9B167F}"/>
-    <cellStyle name="NumericoDerechaDosDecimales" xfId="4" xr:uid="{145F03CC-DC95-40AE-99DF-4610593CB341}"/>
-    <cellStyle name="NumericoIzquierda" xfId="2" xr:uid="{01BCF566-7284-425C-A9A0-3D645BC79117}"/>
-    <cellStyle name="NumericoIzquierdaTresDecimales" xfId="6" xr:uid="{4688073A-F4F0-4107-9E69-1FAABA3B8738}"/>
-    <cellStyle name="TextoIzquierda" xfId="1" xr:uid="{074D1C0F-245D-4AC9-8713-07D73C109C2F}"/>
+    <cellStyle name="NumericoDerecha" xfId="3" xr:uid="{9AA61690-0C81-4FC4-9E77-2146F3F43F44}"/>
+    <cellStyle name="NumericoDerechaCuatroDecimales" xfId="5" xr:uid="{D47A24C5-BE25-405F-B76F-18216FCC5782}"/>
+    <cellStyle name="NumericoDerechaDosDecimales" xfId="4" xr:uid="{D70997C1-DD7D-49C0-9B55-574C230ABE26}"/>
+    <cellStyle name="NumericoIzquierda" xfId="2" xr:uid="{2C8D679C-032A-440A-A77C-CC744EA41BC0}"/>
+    <cellStyle name="NumericoIzquierdaTresDecimales" xfId="6" xr:uid="{F7414BD8-CD89-4A48-B725-95416CA5F959}"/>
+    <cellStyle name="TextoIzquierda" xfId="1" xr:uid="{CD3A3854-EB73-44FA-89B6-7BBC164223B1}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3180,8 +3352,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14670F2B-DBDB-4BD0-9ED7-2E7603949175}">
-  <dimension ref="A1:AO265"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E87B0BA1-55E0-4D7C-B12E-9A782A23B7AC}">
+  <dimension ref="A1:AO289"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="35.28515625" style="1" customWidth="1"/>
@@ -35386,64 +35558,64 @@
         <v>51</v>
       </c>
       <c r="L258" s="1" t="s">
-        <v>481</v>
+        <v>52</v>
       </c>
       <c r="M258" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="N258" s="1" t="s">
         <v>48</v>
       </c>
       <c r="O258" s="1" t="s">
-        <v>48</v>
+        <v>879</v>
       </c>
       <c r="P258" s="2" t="s">
-        <v>879</v>
+        <v>55</v>
       </c>
       <c r="Q258" s="2" t="s">
         <v>880</v>
       </c>
       <c r="R258" s="1" t="s">
-        <v>881</v>
+        <v>360</v>
       </c>
       <c r="S258" s="1" t="s">
-        <v>416</v>
+        <v>361</v>
       </c>
       <c r="T258" s="1" t="s">
-        <v>882</v>
+        <v>362</v>
       </c>
       <c r="U258" s="2">
         <v>0</v>
       </c>
       <c r="V258" s="1" t="s">
-        <v>289</v>
+        <v>60</v>
       </c>
       <c r="W258" s="3">
-        <v>47.79</v>
+        <v>0</v>
       </c>
       <c r="X258" s="2">
         <v>978</v>
       </c>
       <c r="Y258" s="3">
-        <v>81</v>
+        <v>8.2799999999999994</v>
       </c>
       <c r="Z258" s="1" t="s">
         <v>61</v>
       </c>
       <c r="AA258" s="2">
-        <v>183001098</v>
+        <v>183110824</v>
       </c>
       <c r="AB258" s="2">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="AC258" s="1" t="s">
-        <v>290</v>
+        <v>62</v>
       </c>
       <c r="AD258" s="2">
         <v>0</v>
       </c>
       <c r="AE258" s="4" t="s">
-        <v>883</v>
+        <v>63</v>
       </c>
       <c r="AF258" s="3">
         <v>0</v>
@@ -35473,7 +35645,7 @@
         <v>63</v>
       </c>
       <c r="AO258" s="1" t="s">
-        <v>122</v>
+        <v>363</v>
       </c>
     </row>
     <row r="259" spans="1:41" x14ac:dyDescent="0.2">
@@ -35511,64 +35683,64 @@
         <v>51</v>
       </c>
       <c r="L259" s="1" t="s">
-        <v>884</v>
+        <v>52</v>
       </c>
       <c r="M259" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="N259" s="1" t="s">
         <v>48</v>
       </c>
       <c r="O259" s="1" t="s">
-        <v>48</v>
+        <v>881</v>
       </c>
       <c r="P259" s="2" t="s">
-        <v>885</v>
+        <v>55</v>
       </c>
       <c r="Q259" s="2" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="R259" s="1" t="s">
-        <v>887</v>
+        <v>375</v>
       </c>
       <c r="S259" s="1" t="s">
-        <v>888</v>
+        <v>361</v>
       </c>
       <c r="T259" s="1" t="s">
-        <v>889</v>
+        <v>362</v>
       </c>
       <c r="U259" s="2">
-        <v>39950</v>
+        <v>0</v>
       </c>
       <c r="V259" s="1" t="s">
-        <v>890</v>
+        <v>60</v>
       </c>
       <c r="W259" s="3">
-        <v>110.01</v>
+        <v>0</v>
       </c>
       <c r="X259" s="2">
         <v>978</v>
       </c>
       <c r="Y259" s="3">
-        <v>233.22</v>
+        <v>6.83</v>
       </c>
       <c r="Z259" s="1" t="s">
         <v>61</v>
       </c>
       <c r="AA259" s="2">
-        <v>1693</v>
+        <v>183110824</v>
       </c>
       <c r="AB259" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AC259" s="1" t="s">
-        <v>891</v>
+        <v>62</v>
       </c>
       <c r="AD259" s="2">
         <v>0</v>
       </c>
       <c r="AE259" s="4" t="s">
-        <v>892</v>
+        <v>63</v>
       </c>
       <c r="AF259" s="3">
         <v>0</v>
@@ -35598,7 +35770,7 @@
         <v>63</v>
       </c>
       <c r="AO259" s="1" t="s">
-        <v>122</v>
+        <v>376</v>
       </c>
     </row>
     <row r="260" spans="1:41" x14ac:dyDescent="0.2">
@@ -35636,64 +35808,64 @@
         <v>51</v>
       </c>
       <c r="L260" s="1" t="s">
-        <v>411</v>
+        <v>85</v>
       </c>
       <c r="M260" s="1" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="N260" s="1" t="s">
         <v>48</v>
       </c>
       <c r="O260" s="1" t="s">
-        <v>48</v>
+        <v>883</v>
       </c>
       <c r="P260" s="2" t="s">
-        <v>885</v>
+        <v>692</v>
       </c>
       <c r="Q260" s="2" t="s">
-        <v>893</v>
+        <v>884</v>
       </c>
       <c r="R260" s="1" t="s">
-        <v>894</v>
+        <v>232</v>
       </c>
       <c r="S260" s="1" t="s">
-        <v>416</v>
+        <v>233</v>
       </c>
       <c r="T260" s="1" t="s">
-        <v>895</v>
+        <v>234</v>
       </c>
       <c r="U260" s="2">
-        <v>999104</v>
+        <v>0</v>
       </c>
       <c r="V260" s="1" t="s">
-        <v>289</v>
+        <v>60</v>
       </c>
       <c r="W260" s="3">
-        <v>182.94</v>
+        <v>0</v>
       </c>
       <c r="X260" s="2">
         <v>978</v>
       </c>
       <c r="Y260" s="3">
-        <v>321.8</v>
+        <v>17.079999999999998</v>
       </c>
       <c r="Z260" s="1" t="s">
         <v>61</v>
       </c>
       <c r="AA260" s="2">
-        <v>183062793</v>
+        <v>8312738</v>
       </c>
       <c r="AB260" s="2">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="AC260" s="1" t="s">
-        <v>290</v>
+        <v>62</v>
       </c>
       <c r="AD260" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE260" s="4" t="s">
-        <v>896</v>
+        <v>63</v>
       </c>
       <c r="AF260" s="3">
         <v>0</v>
@@ -35723,7 +35895,7 @@
         <v>63</v>
       </c>
       <c r="AO260" s="1" t="s">
-        <v>122</v>
+        <v>235</v>
       </c>
     </row>
     <row r="261" spans="1:41" x14ac:dyDescent="0.2">
@@ -35761,64 +35933,64 @@
         <v>51</v>
       </c>
       <c r="L261" s="1" t="s">
-        <v>884</v>
+        <v>85</v>
       </c>
       <c r="M261" s="1" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="N261" s="1" t="s">
         <v>48</v>
       </c>
       <c r="O261" s="1" t="s">
-        <v>48</v>
+        <v>885</v>
       </c>
       <c r="P261" s="2" t="s">
-        <v>885</v>
+        <v>692</v>
       </c>
       <c r="Q261" s="2" t="s">
-        <v>897</v>
+        <v>886</v>
       </c>
       <c r="R261" s="1" t="s">
-        <v>898</v>
+        <v>260</v>
       </c>
       <c r="S261" s="1" t="s">
-        <v>304</v>
+        <v>233</v>
       </c>
       <c r="T261" s="1" t="s">
-        <v>899</v>
+        <v>234</v>
       </c>
       <c r="U261" s="2">
-        <v>40417</v>
+        <v>0</v>
       </c>
       <c r="V261" s="1" t="s">
-        <v>289</v>
+        <v>60</v>
       </c>
       <c r="W261" s="3">
-        <v>511.74</v>
+        <v>0</v>
       </c>
       <c r="X261" s="2">
         <v>978</v>
       </c>
       <c r="Y261" s="3">
-        <v>900.15</v>
+        <v>10.17</v>
       </c>
       <c r="Z261" s="1" t="s">
         <v>61</v>
       </c>
       <c r="AA261" s="2">
-        <v>183122050</v>
+        <v>8312738</v>
       </c>
       <c r="AB261" s="2">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="AC261" s="1" t="s">
-        <v>290</v>
+        <v>62</v>
       </c>
       <c r="AD261" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE261" s="4" t="s">
-        <v>896</v>
+        <v>63</v>
       </c>
       <c r="AF261" s="3">
         <v>0</v>
@@ -35848,7 +36020,7 @@
         <v>63</v>
       </c>
       <c r="AO261" s="1" t="s">
-        <v>122</v>
+        <v>261</v>
       </c>
     </row>
     <row r="262" spans="1:41" x14ac:dyDescent="0.2">
@@ -35886,64 +36058,64 @@
         <v>51</v>
       </c>
       <c r="L262" s="1" t="s">
-        <v>300</v>
+        <v>85</v>
       </c>
       <c r="M262" s="1" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="N262" s="1" t="s">
         <v>48</v>
       </c>
       <c r="O262" s="1" t="s">
-        <v>48</v>
+        <v>887</v>
       </c>
       <c r="P262" s="2" t="s">
-        <v>885</v>
+        <v>692</v>
       </c>
       <c r="Q262" s="2" t="s">
-        <v>900</v>
+        <v>888</v>
       </c>
       <c r="R262" s="1" t="s">
-        <v>901</v>
+        <v>238</v>
       </c>
       <c r="S262" s="1" t="s">
-        <v>486</v>
+        <v>233</v>
       </c>
       <c r="T262" s="1" t="s">
-        <v>902</v>
+        <v>234</v>
       </c>
       <c r="U262" s="2">
         <v>0</v>
       </c>
       <c r="V262" s="1" t="s">
-        <v>289</v>
+        <v>60</v>
       </c>
       <c r="W262" s="3">
-        <v>300.17</v>
+        <v>0</v>
       </c>
       <c r="X262" s="2">
         <v>978</v>
       </c>
       <c r="Y262" s="3">
-        <v>528</v>
+        <v>3.88</v>
       </c>
       <c r="Z262" s="1" t="s">
         <v>61</v>
       </c>
       <c r="AA262" s="2">
-        <v>183062546</v>
+        <v>8312738</v>
       </c>
       <c r="AB262" s="2">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="AC262" s="1" t="s">
-        <v>290</v>
+        <v>62</v>
       </c>
       <c r="AD262" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE262" s="4" t="s">
-        <v>896</v>
+        <v>63</v>
       </c>
       <c r="AF262" s="3">
         <v>0</v>
@@ -35973,7 +36145,7 @@
         <v>63</v>
       </c>
       <c r="AO262" s="1" t="s">
-        <v>122</v>
+        <v>239</v>
       </c>
     </row>
     <row r="263" spans="1:41" x14ac:dyDescent="0.2">
@@ -36011,31 +36183,31 @@
         <v>51</v>
       </c>
       <c r="L263" s="1" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="M263" s="1" t="s">
-        <v>48</v>
+        <v>482</v>
       </c>
       <c r="N263" s="1" t="s">
         <v>48</v>
       </c>
       <c r="O263" s="1" t="s">
-        <v>48</v>
+        <v>889</v>
       </c>
       <c r="P263" s="2" t="s">
-        <v>885</v>
+        <v>890</v>
       </c>
       <c r="Q263" s="2" t="s">
-        <v>903</v>
+        <v>891</v>
       </c>
       <c r="R263" s="1" t="s">
-        <v>904</v>
+        <v>892</v>
       </c>
       <c r="S263" s="1" t="s">
-        <v>432</v>
+        <v>416</v>
       </c>
       <c r="T263" s="1" t="s">
-        <v>48</v>
+        <v>893</v>
       </c>
       <c r="U263" s="2">
         <v>0</v>
@@ -36044,19 +36216,19 @@
         <v>289</v>
       </c>
       <c r="W263" s="3">
-        <v>275.01</v>
+        <v>47.79</v>
       </c>
       <c r="X263" s="2">
         <v>978</v>
       </c>
       <c r="Y263" s="3">
-        <v>483.74</v>
+        <v>81</v>
       </c>
       <c r="Z263" s="1" t="s">
         <v>61</v>
       </c>
       <c r="AA263" s="2">
-        <v>183054576</v>
+        <v>183001098</v>
       </c>
       <c r="AB263" s="2">
         <v>10</v>
@@ -36068,7 +36240,7 @@
         <v>0</v>
       </c>
       <c r="AE263" s="4" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="AF263" s="3">
         <v>0</v>
@@ -36136,64 +36308,64 @@
         <v>51</v>
       </c>
       <c r="L264" s="1" t="s">
-        <v>488</v>
+        <v>644</v>
       </c>
       <c r="M264" s="1" t="s">
-        <v>48</v>
+        <v>645</v>
       </c>
       <c r="N264" s="1" t="s">
         <v>48</v>
       </c>
       <c r="O264" s="1" t="s">
-        <v>48</v>
+        <v>895</v>
       </c>
       <c r="P264" s="2" t="s">
-        <v>885</v>
+        <v>896</v>
       </c>
       <c r="Q264" s="2" t="s">
-        <v>903</v>
+        <v>897</v>
       </c>
       <c r="R264" s="1" t="s">
-        <v>904</v>
+        <v>303</v>
       </c>
       <c r="S264" s="1" t="s">
-        <v>432</v>
+        <v>304</v>
       </c>
       <c r="T264" s="1" t="s">
-        <v>48</v>
+        <v>305</v>
       </c>
       <c r="U264" s="2">
-        <v>0</v>
+        <v>987610</v>
       </c>
       <c r="V264" s="1" t="s">
-        <v>311</v>
+        <v>289</v>
       </c>
       <c r="W264" s="3">
-        <v>23</v>
+        <v>568.5</v>
       </c>
       <c r="X264" s="2">
         <v>978</v>
       </c>
       <c r="Y264" s="3">
-        <v>37.01</v>
+        <v>1000</v>
       </c>
       <c r="Z264" s="1" t="s">
         <v>61</v>
       </c>
       <c r="AA264" s="2">
-        <v>183054576</v>
+        <v>183059013</v>
       </c>
       <c r="AB264" s="2">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="AC264" s="1" t="s">
-        <v>312</v>
+        <v>290</v>
       </c>
       <c r="AD264" s="2">
         <v>0</v>
       </c>
       <c r="AE264" s="4" t="s">
-        <v>674</v>
+        <v>898</v>
       </c>
       <c r="AF264" s="3">
         <v>0</v>
@@ -36261,64 +36433,64 @@
         <v>51</v>
       </c>
       <c r="L265" s="1" t="s">
-        <v>668</v>
+        <v>899</v>
       </c>
       <c r="M265" s="1" t="s">
-        <v>48</v>
+        <v>900</v>
       </c>
       <c r="N265" s="1" t="s">
         <v>48</v>
       </c>
       <c r="O265" s="1" t="s">
-        <v>48</v>
+        <v>901</v>
       </c>
       <c r="P265" s="2" t="s">
-        <v>885</v>
+        <v>896</v>
       </c>
       <c r="Q265" s="2" t="s">
-        <v>905</v>
+        <v>821</v>
       </c>
       <c r="R265" s="1" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
       <c r="S265" s="1" t="s">
-        <v>233</v>
+        <v>424</v>
       </c>
       <c r="T265" s="1" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="U265" s="2">
         <v>0</v>
       </c>
       <c r="V265" s="1" t="s">
-        <v>289</v>
+        <v>904</v>
       </c>
       <c r="W265" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="X265" s="2">
         <v>978</v>
       </c>
       <c r="Y265" s="3">
-        <v>533.4</v>
+        <v>43.37</v>
       </c>
       <c r="Z265" s="1" t="s">
         <v>61</v>
       </c>
       <c r="AA265" s="2">
-        <v>183050970</v>
+        <v>183125418</v>
       </c>
       <c r="AB265" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AC265" s="1" t="s">
-        <v>290</v>
+        <v>905</v>
       </c>
       <c r="AD265" s="2">
         <v>0</v>
       </c>
       <c r="AE265" s="4" t="s">
-        <v>908</v>
+        <v>63</v>
       </c>
       <c r="AF265" s="3">
         <v>0</v>
@@ -36348,6 +36520,3006 @@
         <v>63</v>
       </c>
       <c r="AO265" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="266" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A266" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B266" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C266" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D266" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E266" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F266" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G266" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H266" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I266" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J266" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K266" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L266" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="M266" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="N266" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="O266" s="1" t="s">
+        <v>906</v>
+      </c>
+      <c r="P266" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="Q266" s="2" t="s">
+        <v>907</v>
+      </c>
+      <c r="R266" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="S266" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="T266" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="U266" s="2">
+        <v>0</v>
+      </c>
+      <c r="V266" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="W266" s="3">
+        <v>0</v>
+      </c>
+      <c r="X266" s="2">
+        <v>978</v>
+      </c>
+      <c r="Y266" s="3">
+        <v>15.5</v>
+      </c>
+      <c r="Z266" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA266" s="2">
+        <v>1</v>
+      </c>
+      <c r="AB266" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC266" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD266" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE266" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AF266" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG266" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH266" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI266" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ266" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK266" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL266" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AM266" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN266" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AO266" s="1" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="267" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A267" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B267" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C267" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D267" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E267" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F267" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G267" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H267" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I267" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J267" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K267" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L267" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="M267" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="N267" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="O267" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="P267" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="Q267" s="2" t="s">
+        <v>909</v>
+      </c>
+      <c r="R267" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="S267" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="T267" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="U267" s="2">
+        <v>0</v>
+      </c>
+      <c r="V267" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="W267" s="3">
+        <v>0</v>
+      </c>
+      <c r="X267" s="2">
+        <v>978</v>
+      </c>
+      <c r="Y267" s="3">
+        <v>15.5</v>
+      </c>
+      <c r="Z267" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA267" s="2">
+        <v>1</v>
+      </c>
+      <c r="AB267" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC267" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD267" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE267" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AF267" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG267" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH267" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI267" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ267" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK267" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL267" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AM267" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN267" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AO267" s="1" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="268" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A268" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B268" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C268" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D268" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E268" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F268" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G268" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H268" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I268" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J268" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K268" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L268" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="M268" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N268" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="O268" s="1" t="s">
+        <v>910</v>
+      </c>
+      <c r="P268" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="Q268" s="2" t="s">
+        <v>911</v>
+      </c>
+      <c r="R268" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="S268" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="T268" s="1" t="s">
+        <v>912</v>
+      </c>
+      <c r="U268" s="2">
+        <v>0</v>
+      </c>
+      <c r="V268" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="W268" s="3">
+        <v>300</v>
+      </c>
+      <c r="X268" s="2">
+        <v>978</v>
+      </c>
+      <c r="Y268" s="3">
+        <v>533.4</v>
+      </c>
+      <c r="Z268" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA268" s="2">
+        <v>183050970</v>
+      </c>
+      <c r="AB268" s="2">
+        <v>10</v>
+      </c>
+      <c r="AC268" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="AD268" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE268" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="AF268" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG268" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH268" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI268" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ268" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK268" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL268" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AM268" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN268" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AO268" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="269" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A269" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B269" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C269" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D269" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E269" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F269" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G269" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H269" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I269" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J269" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K269" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L269" s="1" t="s">
+        <v>914</v>
+      </c>
+      <c r="M269" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N269" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="O269" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P269" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="Q269" s="2" t="s">
+        <v>915</v>
+      </c>
+      <c r="R269" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="S269" s="1" t="s">
+        <v>917</v>
+      </c>
+      <c r="T269" s="1" t="s">
+        <v>918</v>
+      </c>
+      <c r="U269" s="2">
+        <v>39950</v>
+      </c>
+      <c r="V269" s="1" t="s">
+        <v>919</v>
+      </c>
+      <c r="W269" s="3">
+        <v>110.01</v>
+      </c>
+      <c r="X269" s="2">
+        <v>978</v>
+      </c>
+      <c r="Y269" s="3">
+        <v>233.22</v>
+      </c>
+      <c r="Z269" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA269" s="2">
+        <v>1693</v>
+      </c>
+      <c r="AB269" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC269" s="1" t="s">
+        <v>920</v>
+      </c>
+      <c r="AD269" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE269" s="4" t="s">
+        <v>921</v>
+      </c>
+      <c r="AF269" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG269" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH269" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI269" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ269" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK269" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL269" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AM269" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN269" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AO269" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="270" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A270" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B270" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C270" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D270" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E270" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F270" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G270" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H270" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I270" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J270" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K270" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L270" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="M270" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N270" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="O270" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P270" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="Q270" s="2" t="s">
+        <v>922</v>
+      </c>
+      <c r="R270" s="1" t="s">
+        <v>923</v>
+      </c>
+      <c r="S270" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="T270" s="1" t="s">
+        <v>924</v>
+      </c>
+      <c r="U270" s="2">
+        <v>999104</v>
+      </c>
+      <c r="V270" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="W270" s="3">
+        <v>182.94</v>
+      </c>
+      <c r="X270" s="2">
+        <v>978</v>
+      </c>
+      <c r="Y270" s="3">
+        <v>321.8</v>
+      </c>
+      <c r="Z270" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA270" s="2">
+        <v>183062793</v>
+      </c>
+      <c r="AB270" s="2">
+        <v>10</v>
+      </c>
+      <c r="AC270" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="AD270" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE270" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="AF270" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG270" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH270" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI270" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ270" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK270" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL270" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AM270" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN270" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AO270" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="271" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A271" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B271" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C271" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D271" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E271" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F271" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G271" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H271" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I271" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J271" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K271" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L271" s="1" t="s">
+        <v>914</v>
+      </c>
+      <c r="M271" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N271" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="O271" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P271" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="Q271" s="2" t="s">
+        <v>925</v>
+      </c>
+      <c r="R271" s="1" t="s">
+        <v>926</v>
+      </c>
+      <c r="S271" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="T271" s="1" t="s">
+        <v>927</v>
+      </c>
+      <c r="U271" s="2">
+        <v>40417</v>
+      </c>
+      <c r="V271" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="W271" s="3">
+        <v>511.74</v>
+      </c>
+      <c r="X271" s="2">
+        <v>978</v>
+      </c>
+      <c r="Y271" s="3">
+        <v>900.15</v>
+      </c>
+      <c r="Z271" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA271" s="2">
+        <v>183122050</v>
+      </c>
+      <c r="AB271" s="2">
+        <v>10</v>
+      </c>
+      <c r="AC271" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="AD271" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE271" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="AF271" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG271" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH271" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI271" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ271" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK271" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL271" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AM271" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN271" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AO271" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="272" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A272" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B272" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C272" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D272" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E272" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F272" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G272" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H272" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I272" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J272" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K272" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L272" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="M272" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N272" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="O272" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P272" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="Q272" s="2" t="s">
+        <v>928</v>
+      </c>
+      <c r="R272" s="1" t="s">
+        <v>929</v>
+      </c>
+      <c r="S272" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="T272" s="1" t="s">
+        <v>930</v>
+      </c>
+      <c r="U272" s="2">
+        <v>0</v>
+      </c>
+      <c r="V272" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="W272" s="3">
+        <v>300.17</v>
+      </c>
+      <c r="X272" s="2">
+        <v>978</v>
+      </c>
+      <c r="Y272" s="3">
+        <v>528</v>
+      </c>
+      <c r="Z272" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA272" s="2">
+        <v>183062546</v>
+      </c>
+      <c r="AB272" s="2">
+        <v>10</v>
+      </c>
+      <c r="AC272" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="AD272" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE272" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="AF272" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG272" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH272" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI272" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ272" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK272" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL272" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AM272" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN272" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AO272" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="273" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A273" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B273" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C273" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D273" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E273" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F273" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G273" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H273" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I273" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J273" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K273" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L273" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="M273" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N273" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="O273" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P273" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="Q273" s="2" t="s">
+        <v>931</v>
+      </c>
+      <c r="R273" s="1" t="s">
+        <v>932</v>
+      </c>
+      <c r="S273" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="T273" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="U273" s="2">
+        <v>0</v>
+      </c>
+      <c r="V273" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="W273" s="3">
+        <v>275.01</v>
+      </c>
+      <c r="X273" s="2">
+        <v>978</v>
+      </c>
+      <c r="Y273" s="3">
+        <v>483.74</v>
+      </c>
+      <c r="Z273" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA273" s="2">
+        <v>183054576</v>
+      </c>
+      <c r="AB273" s="2">
+        <v>10</v>
+      </c>
+      <c r="AC273" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="AD273" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE273" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="AF273" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG273" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH273" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI273" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ273" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK273" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL273" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AM273" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN273" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AO273" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="274" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A274" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B274" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C274" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D274" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E274" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F274" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G274" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H274" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I274" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J274" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K274" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L274" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="M274" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N274" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="O274" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P274" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="Q274" s="2" t="s">
+        <v>931</v>
+      </c>
+      <c r="R274" s="1" t="s">
+        <v>932</v>
+      </c>
+      <c r="S274" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="T274" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="U274" s="2">
+        <v>0</v>
+      </c>
+      <c r="V274" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="W274" s="3">
+        <v>23</v>
+      </c>
+      <c r="X274" s="2">
+        <v>978</v>
+      </c>
+      <c r="Y274" s="3">
+        <v>37.01</v>
+      </c>
+      <c r="Z274" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA274" s="2">
+        <v>183054576</v>
+      </c>
+      <c r="AB274" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC274" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="AD274" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE274" s="4" t="s">
+        <v>674</v>
+      </c>
+      <c r="AF274" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG274" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH274" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI274" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ274" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK274" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL274" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AM274" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN274" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AO274" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="275" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A275" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B275" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C275" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D275" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E275" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F275" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G275" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H275" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I275" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J275" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K275" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L275" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="M275" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N275" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="O275" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P275" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="Q275" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="R275" s="1" t="s">
+        <v>933</v>
+      </c>
+      <c r="S275" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="T275" s="1" t="s">
+        <v>934</v>
+      </c>
+      <c r="U275" s="2">
+        <v>778313</v>
+      </c>
+      <c r="V275" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="W275" s="3">
+        <v>130.01</v>
+      </c>
+      <c r="X275" s="2">
+        <v>978</v>
+      </c>
+      <c r="Y275" s="3">
+        <v>236.49</v>
+      </c>
+      <c r="Z275" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA275" s="2">
+        <v>183122530</v>
+      </c>
+      <c r="AB275" s="2">
+        <v>10</v>
+      </c>
+      <c r="AC275" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="AD275" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE275" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="AF275" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG275" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH275" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI275" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ275" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK275" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL275" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AM275" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN275" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AO275" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="276" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A276" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B276" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C276" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D276" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E276" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F276" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G276" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H276" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I276" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J276" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K276" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L276" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="M276" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N276" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="O276" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P276" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="Q276" s="2" t="s">
+        <v>935</v>
+      </c>
+      <c r="R276" s="1" t="s">
+        <v>936</v>
+      </c>
+      <c r="S276" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="T276" s="1" t="s">
+        <v>937</v>
+      </c>
+      <c r="U276" s="2">
+        <v>607765</v>
+      </c>
+      <c r="V276" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="W276" s="3">
+        <v>225</v>
+      </c>
+      <c r="X276" s="2">
+        <v>978</v>
+      </c>
+      <c r="Y276" s="3">
+        <v>395.78</v>
+      </c>
+      <c r="Z276" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA276" s="2">
+        <v>183108489</v>
+      </c>
+      <c r="AB276" s="2">
+        <v>10</v>
+      </c>
+      <c r="AC276" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="AD276" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE276" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="AF276" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG276" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH276" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI276" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ276" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK276" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL276" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AM276" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN276" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AO276" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="277" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A277" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B277" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C277" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D277" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E277" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F277" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G277" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H277" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I277" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J277" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K277" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L277" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="M277" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N277" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="O277" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P277" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="Q277" s="2" t="s">
+        <v>935</v>
+      </c>
+      <c r="R277" s="1" t="s">
+        <v>936</v>
+      </c>
+      <c r="S277" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="T277" s="1" t="s">
+        <v>937</v>
+      </c>
+      <c r="U277" s="2">
+        <v>607765</v>
+      </c>
+      <c r="V277" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="W277" s="3">
+        <v>16.02</v>
+      </c>
+      <c r="X277" s="2">
+        <v>978</v>
+      </c>
+      <c r="Y277" s="3">
+        <v>26.58</v>
+      </c>
+      <c r="Z277" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA277" s="2">
+        <v>183108489</v>
+      </c>
+      <c r="AB277" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC277" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="AD277" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE277" s="4" t="s">
+        <v>650</v>
+      </c>
+      <c r="AF277" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG277" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH277" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI277" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ277" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK277" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL277" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AM277" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN277" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AO277" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="278" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A278" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B278" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C278" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D278" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E278" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F278" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G278" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H278" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I278" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J278" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K278" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L278" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="M278" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N278" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="O278" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P278" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="Q278" s="2" t="s">
+        <v>897</v>
+      </c>
+      <c r="R278" s="1" t="s">
+        <v>938</v>
+      </c>
+      <c r="S278" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="T278" s="1" t="s">
+        <v>939</v>
+      </c>
+      <c r="U278" s="2">
+        <v>782962</v>
+      </c>
+      <c r="V278" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="W278" s="3">
+        <v>495.26</v>
+      </c>
+      <c r="X278" s="2">
+        <v>978</v>
+      </c>
+      <c r="Y278" s="3">
+        <v>871.16</v>
+      </c>
+      <c r="Z278" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA278" s="2">
+        <v>183108471</v>
+      </c>
+      <c r="AB278" s="2">
+        <v>10</v>
+      </c>
+      <c r="AC278" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="AD278" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE278" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="AF278" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG278" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH278" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI278" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ278" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK278" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL278" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AM278" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN278" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AO278" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="279" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A279" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B279" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C279" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D279" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E279" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F279" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G279" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H279" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I279" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J279" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K279" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L279" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="M279" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N279" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="O279" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P279" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="Q279" s="2" t="s">
+        <v>897</v>
+      </c>
+      <c r="R279" s="1" t="s">
+        <v>938</v>
+      </c>
+      <c r="S279" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="T279" s="1" t="s">
+        <v>939</v>
+      </c>
+      <c r="U279" s="2">
+        <v>782962</v>
+      </c>
+      <c r="V279" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="W279" s="3">
+        <v>42.52</v>
+      </c>
+      <c r="X279" s="2">
+        <v>978</v>
+      </c>
+      <c r="Y279" s="3">
+        <v>70.540000000000006</v>
+      </c>
+      <c r="Z279" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA279" s="2">
+        <v>183108471</v>
+      </c>
+      <c r="AB279" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC279" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="AD279" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE279" s="4" t="s">
+        <v>650</v>
+      </c>
+      <c r="AF279" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG279" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH279" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI279" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ279" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK279" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL279" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AM279" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN279" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AO279" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="280" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A280" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B280" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C280" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D280" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E280" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F280" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G280" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H280" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I280" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J280" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K280" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L280" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="M280" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N280" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="O280" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P280" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="Q280" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="R280" s="1" t="s">
+        <v>942</v>
+      </c>
+      <c r="S280" s="1" t="s">
+        <v>810</v>
+      </c>
+      <c r="T280" s="1" t="s">
+        <v>943</v>
+      </c>
+      <c r="U280" s="2">
+        <v>0</v>
+      </c>
+      <c r="V280" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="W280" s="3">
+        <v>350</v>
+      </c>
+      <c r="X280" s="2">
+        <v>978</v>
+      </c>
+      <c r="Y280" s="3">
+        <v>619.15</v>
+      </c>
+      <c r="Z280" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA280" s="2">
+        <v>183007194</v>
+      </c>
+      <c r="AB280" s="2">
+        <v>10</v>
+      </c>
+      <c r="AC280" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="AD280" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE280" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="AF280" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG280" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH280" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI280" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ280" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK280" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL280" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AM280" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN280" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AO280" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="281" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A281" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B281" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C281" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D281" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E281" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F281" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G281" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H281" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I281" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J281" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K281" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L281" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="M281" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N281" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="O281" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P281" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="Q281" s="2" t="s">
+        <v>944</v>
+      </c>
+      <c r="R281" s="1" t="s">
+        <v>945</v>
+      </c>
+      <c r="S281" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="T281" s="1" t="s">
+        <v>946</v>
+      </c>
+      <c r="U281" s="2">
+        <v>714820</v>
+      </c>
+      <c r="V281" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="W281" s="3">
+        <v>250.05</v>
+      </c>
+      <c r="X281" s="2">
+        <v>978</v>
+      </c>
+      <c r="Y281" s="3">
+        <v>429.84</v>
+      </c>
+      <c r="Z281" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA281" s="2">
+        <v>183002583</v>
+      </c>
+      <c r="AB281" s="2">
+        <v>10</v>
+      </c>
+      <c r="AC281" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="AD281" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE281" s="4" t="s">
+        <v>947</v>
+      </c>
+      <c r="AF281" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG281" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH281" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI281" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ281" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK281" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL281" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AM281" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN281" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AO281" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="282" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A282" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B282" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C282" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D282" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E282" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F282" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G282" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H282" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I282" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J282" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K282" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L282" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="M282" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N282" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="O282" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P282" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="Q282" s="2" t="s">
+        <v>944</v>
+      </c>
+      <c r="R282" s="1" t="s">
+        <v>945</v>
+      </c>
+      <c r="S282" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="T282" s="1" t="s">
+        <v>946</v>
+      </c>
+      <c r="U282" s="2">
+        <v>714820</v>
+      </c>
+      <c r="V282" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="W282" s="3">
+        <v>31.48</v>
+      </c>
+      <c r="X282" s="2">
+        <v>978</v>
+      </c>
+      <c r="Y282" s="3">
+        <v>31.45</v>
+      </c>
+      <c r="Z282" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA282" s="2">
+        <v>183002583</v>
+      </c>
+      <c r="AB282" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC282" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="AD282" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE282" s="4" t="s">
+        <v>497</v>
+      </c>
+      <c r="AF282" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG282" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH282" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI282" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ282" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK282" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL282" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AM282" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN282" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AO282" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="283" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A283" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B283" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C283" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D283" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E283" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F283" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G283" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H283" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I283" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J283" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K283" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L283" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="M283" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N283" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="O283" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P283" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="Q283" s="2" t="s">
+        <v>948</v>
+      </c>
+      <c r="R283" s="1" t="s">
+        <v>949</v>
+      </c>
+      <c r="S283" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="T283" s="1" t="s">
+        <v>950</v>
+      </c>
+      <c r="U283" s="2">
+        <v>1004114</v>
+      </c>
+      <c r="V283" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="W283" s="3">
+        <v>300</v>
+      </c>
+      <c r="X283" s="2">
+        <v>978</v>
+      </c>
+      <c r="Y283" s="3">
+        <v>523.5</v>
+      </c>
+      <c r="Z283" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA283" s="2">
+        <v>183121136</v>
+      </c>
+      <c r="AB283" s="2">
+        <v>10</v>
+      </c>
+      <c r="AC283" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="AD283" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE283" s="4" t="s">
+        <v>951</v>
+      </c>
+      <c r="AF283" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG283" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH283" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI283" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ283" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK283" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL283" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AM283" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN283" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AO283" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="284" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A284" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B284" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C284" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D284" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E284" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F284" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G284" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H284" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I284" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J284" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K284" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L284" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="M284" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N284" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="O284" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P284" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="Q284" s="2" t="s">
+        <v>952</v>
+      </c>
+      <c r="R284" s="1" t="s">
+        <v>953</v>
+      </c>
+      <c r="S284" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="T284" s="1" t="s">
+        <v>954</v>
+      </c>
+      <c r="U284" s="2">
+        <v>0</v>
+      </c>
+      <c r="V284" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="W284" s="3">
+        <v>51.96</v>
+      </c>
+      <c r="X284" s="2">
+        <v>978</v>
+      </c>
+      <c r="Y284" s="3">
+        <v>86.2</v>
+      </c>
+      <c r="Z284" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA284" s="2">
+        <v>183053024</v>
+      </c>
+      <c r="AB284" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC284" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="AD284" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE284" s="4" t="s">
+        <v>650</v>
+      </c>
+      <c r="AF284" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG284" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH284" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI284" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ284" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK284" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL284" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AM284" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN284" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AO284" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="285" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A285" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B285" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C285" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D285" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E285" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F285" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G285" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H285" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I285" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J285" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K285" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L285" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="M285" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N285" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="O285" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P285" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="Q285" s="2" t="s">
+        <v>955</v>
+      </c>
+      <c r="R285" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="S285" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="T285" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="U285" s="2">
+        <v>35503</v>
+      </c>
+      <c r="V285" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="W285" s="3">
+        <v>500</v>
+      </c>
+      <c r="X285" s="2">
+        <v>978</v>
+      </c>
+      <c r="Y285" s="3">
+        <v>889.5</v>
+      </c>
+      <c r="Z285" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA285" s="2">
+        <v>183130871</v>
+      </c>
+      <c r="AB285" s="2">
+        <v>10</v>
+      </c>
+      <c r="AC285" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="AD285" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE285" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="AF285" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG285" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH285" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI285" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ285" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK285" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL285" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AM285" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN285" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AO285" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="286" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A286" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B286" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C286" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D286" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E286" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F286" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G286" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H286" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I286" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J286" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K286" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L286" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="M286" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N286" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="O286" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P286" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="Q286" s="2" t="s">
+        <v>958</v>
+      </c>
+      <c r="R286" s="1" t="s">
+        <v>959</v>
+      </c>
+      <c r="S286" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="T286" s="1" t="s">
+        <v>960</v>
+      </c>
+      <c r="U286" s="2">
+        <v>0</v>
+      </c>
+      <c r="V286" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="W286" s="3">
+        <v>450.36</v>
+      </c>
+      <c r="X286" s="2">
+        <v>978</v>
+      </c>
+      <c r="Y286" s="3">
+        <v>787.68</v>
+      </c>
+      <c r="Z286" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA286" s="2">
+        <v>183077353</v>
+      </c>
+      <c r="AB286" s="2">
+        <v>10</v>
+      </c>
+      <c r="AC286" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="AD286" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE286" s="4" t="s">
+        <v>961</v>
+      </c>
+      <c r="AF286" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG286" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH286" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI286" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ286" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK286" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL286" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AM286" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN286" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AO286" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="287" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A287" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B287" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C287" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D287" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E287" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F287" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G287" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H287" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I287" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J287" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K287" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L287" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="M287" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N287" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="O287" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P287" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="Q287" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="R287" s="1" t="s">
+        <v>962</v>
+      </c>
+      <c r="S287" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="T287" s="1" t="s">
+        <v>963</v>
+      </c>
+      <c r="U287" s="2">
+        <v>778635</v>
+      </c>
+      <c r="V287" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="W287" s="3">
+        <v>150.15</v>
+      </c>
+      <c r="X287" s="2">
+        <v>978</v>
+      </c>
+      <c r="Y287" s="3">
+        <v>257.51</v>
+      </c>
+      <c r="Z287" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA287" s="2">
+        <v>183105683</v>
+      </c>
+      <c r="AB287" s="2">
+        <v>10</v>
+      </c>
+      <c r="AC287" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="AD287" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE287" s="4" t="s">
+        <v>800</v>
+      </c>
+      <c r="AF287" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG287" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH287" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI287" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ287" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK287" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL287" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AM287" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN287" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AO287" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="288" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A288" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B288" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C288" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D288" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E288" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F288" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G288" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H288" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I288" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J288" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K288" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L288" s="1" t="s">
+        <v>964</v>
+      </c>
+      <c r="M288" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N288" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="O288" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P288" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="Q288" s="2" t="s">
+        <v>965</v>
+      </c>
+      <c r="R288" s="1" t="s">
+        <v>966</v>
+      </c>
+      <c r="S288" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="T288" s="1" t="s">
+        <v>967</v>
+      </c>
+      <c r="U288" s="2">
+        <v>0</v>
+      </c>
+      <c r="V288" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="W288" s="3">
+        <v>34.21</v>
+      </c>
+      <c r="X288" s="2">
+        <v>978</v>
+      </c>
+      <c r="Y288" s="3">
+        <v>37.630000000000003</v>
+      </c>
+      <c r="Z288" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA288" s="2">
+        <v>183076835</v>
+      </c>
+      <c r="AB288" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC288" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="AD288" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE288" s="4" t="s">
+        <v>968</v>
+      </c>
+      <c r="AF288" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG288" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH288" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI288" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ288" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK288" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL288" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AM288" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN288" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AO288" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="289" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A289" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B289" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C289" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D289" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E289" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F289" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G289" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H289" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I289" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J289" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K289" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L289" s="1" t="s">
+        <v>964</v>
+      </c>
+      <c r="M289" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N289" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="O289" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P289" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="Q289" s="2" t="s">
+        <v>965</v>
+      </c>
+      <c r="R289" s="1" t="s">
+        <v>966</v>
+      </c>
+      <c r="S289" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="T289" s="1" t="s">
+        <v>967</v>
+      </c>
+      <c r="U289" s="2">
+        <v>0</v>
+      </c>
+      <c r="V289" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="W289" s="3">
+        <v>413.19</v>
+      </c>
+      <c r="X289" s="2">
+        <v>978</v>
+      </c>
+      <c r="Y289" s="3">
+        <v>706.14</v>
+      </c>
+      <c r="Z289" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA289" s="2">
+        <v>183076835</v>
+      </c>
+      <c r="AB289" s="2">
+        <v>10</v>
+      </c>
+      <c r="AC289" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="AD289" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE289" s="4" t="s">
+        <v>969</v>
+      </c>
+      <c r="AF289" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG289" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH289" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI289" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ289" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK289" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL289" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AM289" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN289" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AO289" s="1" t="s">
         <v>122</v>
       </c>
     </row>
